--- a/results/extra/supplementary_table1_convergent_losses.xlsx
+++ b/results/extra/supplementary_table1_convergent_losses.xlsx
@@ -495,7 +495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Afzoon &amp; Biswal, "Calibrated genome scans find recurrent gene loss in marine and subterranean mammals". Column definitions are in the sheet "Column definitions".</t>
+          <t>Konhar, Afzoon &amp; Biswal, "Calibrated genome scans find recurrent gene loss in marine and subterranean mammals". Column definitions are in the sheet "Column definitions".</t>
         </is>
       </c>
     </row>
